--- a/fbtest1.xlsx
+++ b/fbtest1.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Collection type: posts only</t>
+          <t>Collection type: posts with comments</t>
         </is>
       </c>
     </row>
@@ -474,6 +474,226 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cebuanalhuillierpawnshop/posts/pfbid0jiyH2gDtf49vbeXPaMXRyZ1WjQUxfKiwqZjRabMxaun9AiCwhKkysWyERmMP2LPfl</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cannot detect</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Shares unavailable in active post view; No visible comment samples captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cebuanalhuillierpawnshop/posts/pfbid0SW2UWsfNrqY97sDgH7FnURvGjeyhZ8i8ThXD9r5hWdwVsRswyjBfvDcJ2ibJ5S3Ql</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cannot detect</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Reactions unavailable in active post view; Shares unavailable in active post view; No visible comment samples captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cebuanalhuillierpawnshop/posts/pfbid0ZRowrVLELFyba54Ydksrme13DmYYqiq94GQuxB9GjuC2vaWhQy41W6nKnwMpwgE2l</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cannot detect</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Reactions unavailable in active post view; Shares unavailable in active post view; No visible comment samples captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cebuanalhuillierpawnshop/posts/pfbid02WEb5iJmCYWzcJStHQ6soPduupmbKskWERtfUtrkD65zBDQNmLFZdvbA2m4vFvZ5dl</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cannot detect</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Reactions unavailable in active post view; Shares unavailable in active post view; No visible comment samples captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cebuanalhuillierpawnshop/posts/pfbid02Zh6hQsjciDjvHHmvovbuJVCSSzBxAqz9i4cnbKrmiP7JvjBWU991ZRLiNPCuzTqpl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cannot detect</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Reactions unavailable in active post view; Shares unavailable in active post view; No visible comment samples captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cebuanalhuillierpawnshop/posts/pfbid0g6Qxyw6QmAM5apKYg5tkiMsRVivj3n5hehiyibew9WHcFhfM6KE1Pa1UENv8o6Vtl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cannot detect</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Shares unavailable in active post view; No visible comment samples captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cebuanalhuillierpawnshop/posts/pfbid024jStScGkYjzRPZEui11ChitWfzURqASCDriXCKmEtNRawJVJJXsTRT2Sd8dnW9FKl</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cannot detect</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Reactions unavailable in active post view; Shares unavailable in active post view; No visible comment samples captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cebuanalhuillierpawnshop/posts/pfbid0XyVxL2gDde1CmgGTMzoqKJRMssgEdYXyNx98G5WeiwcdZTmpjeJ5qnkBWCCsuSYMl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cannot detect</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Reactions unavailable in active post view; Shares unavailable in active post view; No visible comment samples captured</t>
         </is>
       </c>
     </row>
